--- a/data/trans_dic/P1803_2016_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1803_2016_2023-Habitat-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,46</t>
+          <t>2,45; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,59</t>
+          <t>4,2; 8,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,31</t>
+          <t>2,28; 5,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,49</t>
+          <t>7,1; 10,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,76</t>
+          <t>2,8; 4,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,75</t>
+          <t>6,2; 8,81</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,76</t>
+          <t>3,16; 5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 64,33</t>
+          <t>5,21; 8,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,34</t>
+          <t>3,48; 6,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,78</t>
+          <t>7,35; 10,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,61</t>
+          <t>3,59; 5,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 45,26</t>
+          <t>6,69; 9,21</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,24</t>
+          <t>2,29; 5,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,81</t>
+          <t>5,16; 9,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,84</t>
+          <t>3,73; 6,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,6</t>
+          <t>8,13; 11,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,37</t>
+          <t>3,21; 5,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,27</t>
+          <t>7,07; 9,65</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,13</t>
+          <t>4,77; 8,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 14,43</t>
+          <t>9,55; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 9,8</t>
+          <t>6,39; 10,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 13,66</t>
+          <t>10,52; 13,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,48</t>
+          <t>6,07; 8,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 13,45</t>
+          <t>10,47; 13,12</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,33</t>
+          <t>3,9; 5,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 33,89</t>
+          <t>7,07; 9,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,37</t>
+          <t>4,79; 6,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,6</t>
+          <t>9,03; 10,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,62</t>
+          <t>4,54; 5,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,36</t>
+          <t>8,4; 9,69</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39773</t>
+          <t>41670</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>62764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97366</t>
+          <t>104433</t>
         </is>
       </c>
     </row>
@@ -1182,32 +1182,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17794; 36871</t>
+          <t>16554; 36873</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28070; 54564</t>
+          <t>29008; 56468</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16141; 35724</t>
+          <t>15339; 35862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47617; 70864</t>
+          <t>51978; 77323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37526; 64164</t>
+          <t>37774; 66343</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82196; 114648</t>
+          <t>88293; 125321</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>312399</t>
+          <t>72460</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86546</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>398945</t>
+          <t>166568</t>
         </is>
       </c>
     </row>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30848; 58923</t>
+          <t>32359; 59771</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77679; 767311</t>
+          <t>54666; 93706</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35736; 66130</t>
+          <t>36332; 63946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71569; 103242</t>
+          <t>78686; 111059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75472; 115839</t>
+          <t>74166; 113524</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>167580; 973546</t>
+          <t>141780; 195281</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72043</t>
+          <t>78591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>123144</t>
+          <t>133606</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1418,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17611; 39808</t>
+          <t>17404; 39259</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37511; 69148</t>
+          <t>41449; 73473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28405; 53685</t>
+          <t>29288; 53849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36738; 98856</t>
+          <t>66027; 95053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>51065; 82869</t>
+          <t>49520; 82220</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83800; 151719</t>
+          <t>114177; 155745</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>111235</t>
+          <t>112852</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129709</t>
+          <t>135344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>240944</t>
+          <t>248196</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45106; 76179</t>
+          <t>44707; 76690</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92873; 133781</t>
+          <t>94596; 136293</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65701; 102316</t>
+          <t>66650; 104731</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103051; 149502</t>
+          <t>117668; 155998</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>121352; 168026</t>
+          <t>120245; 166948</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>210469; 271773</t>
+          <t>220845; 276653</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345891</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>860399</t>
+          <t>652803</t>
         </is>
       </c>
     </row>
@@ -1654,32 +1654,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>130818; 180874</t>
+          <t>132226; 181067</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>278006; 1172526</t>
+          <t>249779; 322394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166982; 225840</t>
+          <t>169707; 223109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>283016; 387944</t>
+          <t>337119; 401514</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>312431; 390129</t>
+          <t>315049; 391061</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>619385; 1663521</t>
+          <t>610512; 704185</t>
         </is>
       </c>
     </row>
